--- a/rsvp_forms/011_military_appreciation_event_registration--rsvp_forms.xlsx
+++ b/rsvp_forms/011_military_appreciation_event_registration--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'army',_'value':_'army'}</t>
+          <t>army</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Army', 'value': 'Army'}</t>
+          <t>Army</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'navy',_'value':_'navy'}</t>
+          <t>navy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Navy', 'value': 'Navy'}</t>
+          <t>Navy</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'air_force',_'value':_'air_force'}</t>
+          <t>air_force</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Air Force', 'value': 'Air Force'}</t>
+          <t>Air Force</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'marine_corps',_'value':_'marine_corps'}</t>
+          <t>marine_corps</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Marine Corps', 'value': 'Marine Corps'}</t>
+          <t>Marine Corps</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'coast_guard',_'value':_'coast_guard'}</t>
+          <t>coast_guard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Coast Guard', 'value': 'Coast Guard'}</t>
+          <t>Coast Guard</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_sure',_'value':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Sure', 'value': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Online', 'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'location_1',_'value':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Location 1', 'value': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'location_2',_'value':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Location 2', 'value': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'location_3',_'value':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Location 3', 'value': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'location_4',_'value':_'location_4'}</t>
+          <t>location_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Location 4', 'value': 'Location 4'}</t>
+          <t>Location 4</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'location_5',_'value':_'location_5'}</t>
+          <t>location_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Location 5', 'value': 'Location 5'}</t>
+          <t>Location 5</t>
         </is>
       </c>
     </row>
